--- a/indicadores/ARG-MSS_out.xlsx
+++ b/indicadores/ARG-MSS_out.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Importaciones de servicios de Argentina</t>
+    <t xml:space="preserve">Egresos por servicios de Argentina</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
